--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:39</t>
+    <t xml:space="preserve">2026-09-09 22:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:25</t>
+    <t xml:space="preserve">2026-09-12 19:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_los rios.xlsx
@@ -42,12 +42,12 @@
     <t xml:space="preserve">Corral</t>
   </si>
   <si>
+    <t xml:space="preserve">Lago Ranco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Máfil</t>
   </si>
   <si>
-    <t xml:space="preserve">Lago Ranco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Los Lagos</t>
   </si>
   <si>
@@ -57,12 +57,12 @@
     <t xml:space="preserve">Futrono</t>
   </si>
   <si>
+    <t xml:space="preserve">Lanco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mariquina</t>
   </si>
   <si>
-    <t xml:space="preserve">Lanco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Panguipulli</t>
   </si>
   <si>
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:42</t>
+    <t xml:space="preserve">2026-09-24 00:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -517,7 +517,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>73.88</v>
+        <v>25.28</v>
       </c>
     </row>
     <row r="3">
@@ -534,7 +534,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>44.8</v>
+        <v>21.49</v>
       </c>
     </row>
     <row r="4">
@@ -545,13 +545,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>14105</v>
+        <v>14203</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>39.9</v>
+        <v>17.58</v>
       </c>
     </row>
     <row r="5">
@@ -562,13 +562,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>14203</v>
+        <v>14105</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>39.66</v>
+        <v>17.33</v>
       </c>
     </row>
     <row r="6">
@@ -585,7 +585,7 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>35.37</v>
+        <v>16.53</v>
       </c>
     </row>
     <row r="7">
@@ -602,7 +602,7 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>33</v>
+        <v>15.78</v>
       </c>
     </row>
     <row r="8">
@@ -619,7 +619,7 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>32.87</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="9">
@@ -630,13 +630,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>14106</v>
+        <v>14103</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>32.35</v>
+        <v>14.68</v>
       </c>
     </row>
     <row r="10">
@@ -647,13 +647,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>14103</v>
+        <v>14106</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>31.71</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="11">
@@ -670,7 +670,7 @@
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>30.93</v>
+        <v>14.44</v>
       </c>
     </row>
     <row r="12">
@@ -687,7 +687,7 @@
         <v>2023</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>27.55</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -704,7 +704,7 @@
         <v>2023</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>26.14</v>
+        <v>10.99</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:19</t>
+    <t xml:space="preserve">2026-09-27 22:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:08</t>
+    <t xml:space="preserve">2026-09-29 11:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -517,7 +517,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>25.28</v>
+        <v>252.77</v>
       </c>
     </row>
     <row r="3">
@@ -534,7 +534,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>21.49</v>
+        <v>214.89</v>
       </c>
     </row>
     <row r="4">
@@ -551,7 +551,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>17.58</v>
+        <v>175.82</v>
       </c>
     </row>
     <row r="5">
@@ -568,7 +568,7 @@
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>17.33</v>
+        <v>173.33</v>
       </c>
     </row>
     <row r="6">
@@ -585,7 +585,7 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>16.53</v>
+        <v>165.32</v>
       </c>
     </row>
     <row r="7">
@@ -602,7 +602,7 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>15.78</v>
+        <v>157.77</v>
       </c>
     </row>
     <row r="8">
@@ -619,7 +619,7 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>15.05</v>
+        <v>150.49</v>
       </c>
     </row>
     <row r="9">
@@ -636,7 +636,7 @@
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>14.68</v>
+        <v>146.76</v>
       </c>
     </row>
     <row r="10">
@@ -653,7 +653,7 @@
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>14.59</v>
+        <v>145.93</v>
       </c>
     </row>
     <row r="11">
@@ -670,7 +670,7 @@
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>14.44</v>
+        <v>144.39</v>
       </c>
     </row>
     <row r="12">
@@ -687,7 +687,7 @@
         <v>2023</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>12</v>
+        <v>119.99</v>
       </c>
     </row>
     <row r="13">
@@ -704,7 +704,7 @@
         <v>2023</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>10.99</v>
+        <v>109.92</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:03</t>
+    <t xml:space="preserve">2026-10-01 19:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:28</t>
+    <t xml:space="preserve">2026-10-02 13:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:15</t>
+    <t xml:space="preserve">2026-10-05 07:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
